--- a/Reference_seqs/HCV_Subtype_Refs_Without_Comet_Consensus.xlsx
+++ b/Reference_seqs/HCV_Subtype_Refs_Without_Comet_Consensus.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6xb</t>
+          <t>6u</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JX183552</t>
+          <t>EU246940</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KJ567645</t>
+          <t>JX183552</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6xc</t>
+          <t>6xb</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KJ567651</t>
+          <t>KJ567645</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>6xd</t>
+          <t>6xc</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KM252789</t>
+          <t>KJ567651</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KM252790</t>
+          <t>KM252789</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6xe</t>
+          <t>6xd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JX183557</t>
+          <t>KM252790</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KM252792</t>
+          <t>JX183557</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6xf</t>
+          <t>6xe</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KJ567646</t>
+          <t>KM252792</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KJ567647</t>
+          <t>KJ567646</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6xg</t>
+          <t>6xf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MH492360</t>
+          <t>KJ567647</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MH492361</t>
+          <t>MH492360</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>6xh</t>
+          <t>6xg</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MG879000</t>
+          <t>MH492361</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6xi</t>
+          <t>6xh</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JX183549</t>
+          <t>MG879000</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MZ504973</t>
+          <t>JX183549</t>
         </is>
       </c>
     </row>
@@ -1979,34 +1979,34 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>6xj</t>
+          <t>6xi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MZ171127</t>
+          <t>MZ504973</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NS5B</t>
+          <t>NS5A_NTD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GT1</t>
+          <t>GT6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1i</t>
+          <t>6xj</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KJ439772</t>
+          <t>MZ171127</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1j</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KJ439773</t>
+          <t>KJ439772</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>1j</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KJ439774</t>
+          <t>KJ439773</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KJ439778</t>
+          <t>KJ439774</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KJ439782</t>
+          <t>KJ439778</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KJ439775</t>
+          <t>KJ439782</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KJ439781</t>
+          <t>KJ439775</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KJ439779</t>
+          <t>KJ439781</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MH885469</t>
+          <t>KJ439779</t>
         </is>
       </c>
     </row>
@@ -2194,17 +2194,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GT2</t>
+          <t>GT1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JF735120</t>
+          <t>MH885469</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2f</t>
+          <t>2e</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KC844042</t>
+          <t>JF735120</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KC844050</t>
+          <t>KC844042</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2i</t>
+          <t>2f</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DQ155561</t>
+          <t>KC844050</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2l</t>
+          <t>2i</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KC197235</t>
+          <t>DQ155561</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KC197240</t>
+          <t>KC197235</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>2l</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>JF735111</t>
+          <t>KC197240</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>JX227967</t>
+          <t>JF735111</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2q</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FN666428</t>
+          <t>JX227967</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FN666429</t>
+          <t>FN666428</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2r</t>
+          <t>2q</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>JF735115</t>
+          <t>FN666429</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2t</t>
+          <t>2r</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KC197238</t>
+          <t>JF735115</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>2t</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>JF735112</t>
+          <t>KC197238</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2v</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MW041295</t>
+          <t>JF735112</t>
         </is>
       </c>
     </row>
@@ -2502,17 +2502,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GT3</t>
+          <t>GT2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2v</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KJ470619</t>
+          <t>MW041295</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KJ470618</t>
+          <t>KJ470619</t>
         </is>
       </c>
     </row>
@@ -2546,17 +2546,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GT4</t>
+          <t>GT3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4s</t>
+          <t>3e</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>JF735136</t>
+          <t>KJ470618</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GT5</t>
+          <t>GT4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5b</t>
+          <t>4s</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PQ899568</t>
+          <t>JF735136</t>
         </is>
       </c>
     </row>
@@ -2590,17 +2590,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GT6</t>
+          <t>GT5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6xb</t>
+          <t>5b</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JX183552</t>
+          <t>PQ899568</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KJ567645</t>
+          <t>JX183552</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>6xc</t>
+          <t>6xb</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KJ567651</t>
+          <t>KJ567645</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>6xd</t>
+          <t>6xc</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KM252789</t>
+          <t>KJ567651</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KM252790</t>
+          <t>KM252789</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>6xe</t>
+          <t>6xd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>JX183557</t>
+          <t>KM252790</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>KM252792</t>
+          <t>JX183557</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>6xf</t>
+          <t>6xe</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>KJ567646</t>
+          <t>KM252792</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>KJ567647</t>
+          <t>KJ567646</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>6xg</t>
+          <t>6xf</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MH492360</t>
+          <t>KJ567647</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MH492361</t>
+          <t>MH492360</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>6xh</t>
+          <t>6xg</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MG879000</t>
+          <t>MH492361</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>6xi</t>
+          <t>6xh</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>JX183549</t>
+          <t>MG879000</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MZ504973</t>
+          <t>JX183549</t>
         </is>
       </c>
     </row>
@@ -2903,10 +2903,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>6xi</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>MZ504973</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NS5B</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GT6</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>6xj</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>MZ171127</t>
         </is>

--- a/Reference_seqs/HCV_Subtype_Refs_Without_Comet_Consensus.xlsx
+++ b/Reference_seqs/HCV_Subtype_Refs_Without_Comet_Consensus.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1221,22 +1221,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NS5A_NTD</t>
+          <t>NS3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GT1</t>
+          <t>GT7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1i</t>
+          <t>7b</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KJ439772</t>
+          <t>KX092342</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1j</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KJ439773</t>
+          <t>KJ439772</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>1j</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KJ439774</t>
+          <t>KJ439773</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KJ439778</t>
+          <t>KJ439774</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KJ439782</t>
+          <t>KJ439778</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KJ439775</t>
+          <t>KJ439782</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KJ439781</t>
+          <t>KJ439775</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KJ439779</t>
+          <t>KJ439781</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MH885469</t>
+          <t>KJ439779</t>
         </is>
       </c>
     </row>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GT2</t>
+          <t>GT1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2f</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KC844042</t>
+          <t>MH885469</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KC844050</t>
+          <t>KC844042</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2l</t>
+          <t>2f</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KC197235</t>
+          <t>KC844050</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KC197240</t>
+          <t>KC197235</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2t</t>
+          <t>2l</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KC197238</t>
+          <t>KC197240</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>2t</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JF735112</t>
+          <t>KC197238</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2v</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MW041295</t>
+          <t>JF735112</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GT3</t>
+          <t>GT2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2v</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KJ470619</t>
+          <t>MW041295</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KJ470618</t>
+          <t>KJ470619</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GT4</t>
+          <t>GT3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4s</t>
+          <t>3e</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JF735136</t>
+          <t>KJ470618</t>
         </is>
       </c>
     </row>
@@ -1644,17 +1644,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GT5</t>
+          <t>GT4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5b</t>
+          <t>4s</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PQ899568</t>
+          <t>JF735136</t>
         </is>
       </c>
     </row>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GT6</t>
+          <t>GT5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6u</t>
+          <t>5b</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EU246940</t>
+          <t>PQ899568</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6xb</t>
+          <t>6u</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>JX183552</t>
+          <t>EU246940</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KJ567645</t>
+          <t>JX183552</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>6xc</t>
+          <t>6xb</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KJ567651</t>
+          <t>KJ567645</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>6xd</t>
+          <t>6xc</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KM252789</t>
+          <t>KJ567651</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KM252790</t>
+          <t>KM252789</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6xe</t>
+          <t>6xd</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>JX183557</t>
+          <t>KM252790</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KM252792</t>
+          <t>JX183557</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6xf</t>
+          <t>6xe</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KJ567646</t>
+          <t>KM252792</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KJ567647</t>
+          <t>KJ567646</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6xg</t>
+          <t>6xf</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MH492360</t>
+          <t>KJ567647</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MH492361</t>
+          <t>MH492360</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6xh</t>
+          <t>6xg</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MG879000</t>
+          <t>MH492361</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>6xi</t>
+          <t>6xh</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JX183549</t>
+          <t>MG879000</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MZ504973</t>
+          <t>JX183549</t>
         </is>
       </c>
     </row>
@@ -2001,34 +2001,34 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>6xj</t>
+          <t>6xi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MZ171127</t>
+          <t>MZ504973</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NS5B</t>
+          <t>NS5A_NTD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GT1</t>
+          <t>GT6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1i</t>
+          <t>6xj</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KJ439772</t>
+          <t>MZ171127</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1j</t>
+          <t>1i</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KJ439773</t>
+          <t>KJ439772</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>1j</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KJ439774</t>
+          <t>KJ439773</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KJ439778</t>
+          <t>KJ439774</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KJ439782</t>
+          <t>KJ439778</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1n</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KJ439775</t>
+          <t>KJ439782</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KJ439781</t>
+          <t>KJ439775</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1o</t>
+          <t>1n</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KJ439779</t>
+          <t>KJ439781</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MH885469</t>
+          <t>KJ439779</t>
         </is>
       </c>
     </row>
@@ -2216,17 +2216,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GT2</t>
+          <t>GT1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>1o</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JF735120</t>
+          <t>MH885469</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2f</t>
+          <t>2e</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KC844042</t>
+          <t>JF735120</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KC844050</t>
+          <t>KC844042</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2i</t>
+          <t>2f</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DQ155561</t>
+          <t>KC844050</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2l</t>
+          <t>2i</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KC197235</t>
+          <t>DQ155561</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KC197240</t>
+          <t>KC197235</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>2l</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>JF735111</t>
+          <t>KC197240</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>JX227967</t>
+          <t>JF735111</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2q</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FN666428</t>
+          <t>JX227967</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FN666429</t>
+          <t>FN666428</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2r</t>
+          <t>2q</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>JF735115</t>
+          <t>FN666429</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2t</t>
+          <t>2r</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KC197238</t>
+          <t>JF735115</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>2t</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>JF735112</t>
+          <t>KC197238</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2v</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MW041295</t>
+          <t>JF735112</t>
         </is>
       </c>
     </row>
@@ -2524,17 +2524,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GT3</t>
+          <t>GT2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>2v</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KJ470619</t>
+          <t>MW041295</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KJ470618</t>
+          <t>KJ470619</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GT4</t>
+          <t>GT3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>4s</t>
+          <t>3e</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>JF735136</t>
+          <t>KJ470618</t>
         </is>
       </c>
     </row>
@@ -2590,17 +2590,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GT5</t>
+          <t>GT4</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>5b</t>
+          <t>4s</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PQ899568</t>
+          <t>JF735136</t>
         </is>
       </c>
     </row>
@@ -2612,17 +2612,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GT6</t>
+          <t>GT5</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>6xb</t>
+          <t>5b</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>JX183552</t>
+          <t>PQ899568</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KJ567645</t>
+          <t>JX183552</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>6xc</t>
+          <t>6xb</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KJ567651</t>
+          <t>KJ567645</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>6xd</t>
+          <t>6xc</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KM252789</t>
+          <t>KJ567651</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KM252790</t>
+          <t>KM252789</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2727,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>6xe</t>
+          <t>6xd</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>JX183557</t>
+          <t>KM252790</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>KM252792</t>
+          <t>JX183557</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>6xf</t>
+          <t>6xe</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>KJ567646</t>
+          <t>KM252792</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KJ567647</t>
+          <t>KJ567646</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>6xg</t>
+          <t>6xf</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MH492360</t>
+          <t>KJ567647</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MH492361</t>
+          <t>MH492360</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>6xh</t>
+          <t>6xg</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>MG879000</t>
+          <t>MH492361</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>6xi</t>
+          <t>6xh</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>JX183549</t>
+          <t>MG879000</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>MZ504973</t>
+          <t>JX183549</t>
         </is>
       </c>
     </row>
@@ -2925,10 +2925,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>6xi</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>MZ504973</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NS5B</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GT6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
           <t>6xj</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>MZ171127</t>
         </is>
